--- a/artfynd/A 38096-2024 artfynd.xlsx
+++ b/artfynd/A 38096-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119787643</v>
+        <v>119787921</v>
       </c>
       <c r="B3" t="n">
         <v>100144</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599687</v>
+        <v>599666</v>
       </c>
       <c r="R3" t="n">
-        <v>7046769</v>
+        <v>7046725</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119787921</v>
+        <v>119787692</v>
       </c>
       <c r="B5" t="n">
-        <v>100144</v>
+        <v>95202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599666</v>
+        <v>599682</v>
       </c>
       <c r="R5" t="n">
-        <v>7046725</v>
+        <v>7046769</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119787954</v>
+        <v>119787841</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>100144</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599678</v>
+        <v>599666</v>
       </c>
       <c r="R6" t="n">
-        <v>7046719</v>
+        <v>7046735</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119787692</v>
+        <v>119787643</v>
       </c>
       <c r="B7" t="n">
-        <v>95202</v>
+        <v>100144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599682</v>
+        <v>599687</v>
       </c>
       <c r="R7" t="n">
         <v>7046769</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119787841</v>
+        <v>119787954</v>
       </c>
       <c r="B8" t="n">
-        <v>100144</v>
+        <v>79607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1365</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599666</v>
+        <v>599678</v>
       </c>
       <c r="R8" t="n">
-        <v>7046735</v>
+        <v>7046719</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 38096-2024 artfynd.xlsx
+++ b/artfynd/A 38096-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119787817</v>
+        <v>119787921</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>100144</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599654</v>
+        <v>599666</v>
       </c>
       <c r="R2" t="n">
-        <v>7046737</v>
+        <v>7046725</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119787921</v>
+        <v>119787841</v>
       </c>
       <c r="B3" t="n">
         <v>100144</v>
@@ -820,10 +820,10 @@
         <v>599666</v>
       </c>
       <c r="R3" t="n">
-        <v>7046725</v>
+        <v>7046735</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119787801</v>
+        <v>119787643</v>
       </c>
       <c r="B4" t="n">
-        <v>95202</v>
+        <v>100144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599664</v>
+        <v>599687</v>
       </c>
       <c r="R4" t="n">
-        <v>7046728</v>
+        <v>7046769</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119787692</v>
+        <v>119787801</v>
       </c>
       <c r="B5" t="n">
         <v>95202</v>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599682</v>
+        <v>599664</v>
       </c>
       <c r="R5" t="n">
-        <v>7046769</v>
+        <v>7046728</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119787841</v>
+        <v>119787954</v>
       </c>
       <c r="B6" t="n">
-        <v>100144</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599666</v>
+        <v>599678</v>
       </c>
       <c r="R6" t="n">
-        <v>7046735</v>
+        <v>7046719</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119787643</v>
+        <v>119787692</v>
       </c>
       <c r="B7" t="n">
-        <v>100144</v>
+        <v>95202</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599687</v>
+        <v>599682</v>
       </c>
       <c r="R7" t="n">
         <v>7046769</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119787954</v>
+        <v>119787817</v>
       </c>
       <c r="B8" t="n">
         <v>79607</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599678</v>
+        <v>599654</v>
       </c>
       <c r="R8" t="n">
-        <v>7046719</v>
+        <v>7046737</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 38096-2024 artfynd.xlsx
+++ b/artfynd/A 38096-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119787921</v>
+        <v>119787801</v>
       </c>
       <c r="B2" t="n">
-        <v>100144</v>
+        <v>95202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599666</v>
+        <v>599664</v>
       </c>
       <c r="R2" t="n">
-        <v>7046725</v>
+        <v>7046728</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119787841</v>
+        <v>119787921</v>
       </c>
       <c r="B3" t="n">
         <v>100144</v>
@@ -820,10 +820,10 @@
         <v>599666</v>
       </c>
       <c r="R3" t="n">
-        <v>7046735</v>
+        <v>7046725</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119787643</v>
+        <v>119787954</v>
       </c>
       <c r="B4" t="n">
-        <v>100144</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599687</v>
+        <v>599678</v>
       </c>
       <c r="R4" t="n">
-        <v>7046769</v>
+        <v>7046719</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119787801</v>
+        <v>119787817</v>
       </c>
       <c r="B5" t="n">
-        <v>95202</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599664</v>
+        <v>599654</v>
       </c>
       <c r="R5" t="n">
-        <v>7046728</v>
+        <v>7046737</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119787954</v>
+        <v>119787643</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>100144</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599678</v>
+        <v>599687</v>
       </c>
       <c r="R6" t="n">
-        <v>7046719</v>
+        <v>7046769</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119787817</v>
+        <v>119787841</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>100144</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599654</v>
+        <v>599666</v>
       </c>
       <c r="R8" t="n">
-        <v>7046737</v>
+        <v>7046735</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 38096-2024 artfynd.xlsx
+++ b/artfynd/A 38096-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119787801</v>
       </c>
       <c r="B2" t="n">
-        <v>95202</v>
+        <v>95225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119787921</v>
+        <v>119787841</v>
       </c>
       <c r="B3" t="n">
-        <v>100144</v>
+        <v>100167</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         <v>599666</v>
       </c>
       <c r="R3" t="n">
-        <v>7046725</v>
+        <v>7046735</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119787954</v>
+        <v>119787817</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599678</v>
+        <v>599654</v>
       </c>
       <c r="R4" t="n">
-        <v>7046719</v>
+        <v>7046737</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119787817</v>
+        <v>119787954</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599654</v>
+        <v>599678</v>
       </c>
       <c r="R5" t="n">
-        <v>7046737</v>
+        <v>7046719</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119787643</v>
+        <v>119787921</v>
       </c>
       <c r="B6" t="n">
-        <v>100144</v>
+        <v>100167</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599687</v>
+        <v>599666</v>
       </c>
       <c r="R6" t="n">
-        <v>7046769</v>
+        <v>7046725</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>119787692</v>
       </c>
       <c r="B7" t="n">
-        <v>95202</v>
+        <v>95225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119787841</v>
+        <v>119787643</v>
       </c>
       <c r="B8" t="n">
-        <v>100144</v>
+        <v>100167</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599666</v>
+        <v>599687</v>
       </c>
       <c r="R8" t="n">
-        <v>7046735</v>
+        <v>7046769</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 38096-2024 artfynd.xlsx
+++ b/artfynd/A 38096-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119787841</v>
+        <v>119787817</v>
       </c>
       <c r="B3" t="n">
-        <v>100167</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1365</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599666</v>
+        <v>599654</v>
       </c>
       <c r="R3" t="n">
-        <v>7046735</v>
+        <v>7046737</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119787817</v>
+        <v>119787921</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>100167</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599654</v>
+        <v>599666</v>
       </c>
       <c r="R4" t="n">
-        <v>7046737</v>
+        <v>7046725</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119787954</v>
+        <v>119787841</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>100167</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599678</v>
+        <v>599666</v>
       </c>
       <c r="R5" t="n">
-        <v>7046719</v>
+        <v>7046735</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119787921</v>
+        <v>119787954</v>
       </c>
       <c r="B6" t="n">
-        <v>100167</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599666</v>
+        <v>599678</v>
       </c>
       <c r="R6" t="n">
-        <v>7046725</v>
+        <v>7046719</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
